--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,6 +963,861 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118870527</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>456546</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6650834</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118870537</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>456603</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6651057</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118870533</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90469</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456624</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6651012</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118870528</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456560</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6650873</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118870536</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456606</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6651051</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118870530</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456548</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6650892</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118870529</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90451</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>112</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>456556</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6650879</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118870532</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kullbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>456562</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6650919</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -965,10 +965,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118870527</v>
+        <v>118870530</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,37 +981,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456546</v>
+        <v>456548</v>
       </c>
       <c r="R4" t="n">
-        <v>6650834</v>
+        <v>6650892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1052,24 +1049,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118870537</v>
+        <v>118870529</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>90451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,21 +1083,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1126,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456603</v>
+        <v>456556</v>
       </c>
       <c r="R5" t="n">
-        <v>6651057</v>
+        <v>6650879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,6 +1153,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1188,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118870533</v>
+        <v>118870536</v>
       </c>
       <c r="B6" t="n">
-        <v>90469</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,38 +1196,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456624</v>
+        <v>456606</v>
       </c>
       <c r="R6" t="n">
-        <v>6651012</v>
+        <v>6651051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1290,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118870528</v>
+        <v>118870532</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,25 +1303,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1330,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456560</v>
+        <v>456562</v>
       </c>
       <c r="R7" t="n">
-        <v>6650873</v>
+        <v>6650919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118870536</v>
+        <v>118870533</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>90469</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,43 +1405,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456606</v>
+        <v>456624</v>
       </c>
       <c r="R8" t="n">
-        <v>6651051</v>
+        <v>6651012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118870530</v>
+        <v>118870537</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1539,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456548</v>
+        <v>456603</v>
       </c>
       <c r="R9" t="n">
-        <v>6650892</v>
+        <v>6651057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118870529</v>
+        <v>118870528</v>
       </c>
       <c r="B10" t="n">
-        <v>90451</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1613,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456556</v>
+        <v>456560</v>
       </c>
       <c r="R10" t="n">
-        <v>6650879</v>
+        <v>6650873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,21 +1683,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118870532</v>
+        <v>118870527</v>
       </c>
       <c r="B11" t="n">
-        <v>97763</v>
+        <v>79565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1711,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456562</v>
+        <v>456546</v>
       </c>
       <c r="R11" t="n">
-        <v>6650919</v>
+        <v>6650834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,8 +1786,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -1067,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118870529</v>
+        <v>118870536</v>
       </c>
       <c r="B5" t="n">
-        <v>90451</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,34 +1083,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456556</v>
+        <v>456606</v>
       </c>
       <c r="R5" t="n">
-        <v>6650879</v>
+        <v>6651051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,21 +1158,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1184,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118870536</v>
+        <v>118870537</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,39 +1190,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456606</v>
+        <v>456603</v>
       </c>
       <c r="R6" t="n">
-        <v>6651051</v>
+        <v>6651057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1291,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118870532</v>
+        <v>118870533</v>
       </c>
       <c r="B7" t="n">
-        <v>97763</v>
+        <v>90469</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,21 +1292,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1331,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456562</v>
+        <v>456624</v>
       </c>
       <c r="R7" t="n">
-        <v>6650919</v>
+        <v>6651012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118870533</v>
+        <v>118870527</v>
       </c>
       <c r="B8" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,38 +1390,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456624</v>
+        <v>456546</v>
       </c>
       <c r="R8" t="n">
-        <v>6651012</v>
+        <v>6650834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,8 +1465,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1495,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118870537</v>
+        <v>118870532</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>97763</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,25 +1511,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1535,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456603</v>
+        <v>456562</v>
       </c>
       <c r="R9" t="n">
-        <v>6651057</v>
+        <v>6650919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118870528</v>
+        <v>118870529</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>90451</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1617,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456560</v>
+        <v>456556</v>
       </c>
       <c r="R10" t="n">
-        <v>6650873</v>
+        <v>6650879</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,6 +1687,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1699,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118870527</v>
+        <v>118870528</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,37 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456546</v>
+        <v>456560</v>
       </c>
       <c r="R11" t="n">
-        <v>6650834</v>
+        <v>6650873</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,24 +1802,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -965,10 +965,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118870530</v>
+        <v>118870528</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456548</v>
+        <v>456560</v>
       </c>
       <c r="R4" t="n">
-        <v>6650892</v>
+        <v>6650873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118870536</v>
+        <v>118870532</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>97770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,43 +1079,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456606</v>
+        <v>456562</v>
       </c>
       <c r="R5" t="n">
-        <v>6651051</v>
+        <v>6650919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1177,7 +1172,7 @@
         <v>118870537</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1276,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118870533</v>
+        <v>118870536</v>
       </c>
       <c r="B7" t="n">
-        <v>90469</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,38 +1283,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456624</v>
+        <v>456606</v>
       </c>
       <c r="R7" t="n">
-        <v>6651012</v>
+        <v>6651051</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118870527</v>
+        <v>118870529</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>90458</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,37 +1394,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456546</v>
+        <v>456556</v>
       </c>
       <c r="R8" t="n">
-        <v>6650834</v>
+        <v>6650879</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,23 +1462,22 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1499,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118870532</v>
+        <v>118870527</v>
       </c>
       <c r="B9" t="n">
-        <v>97763</v>
+        <v>79572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,38 +1507,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456562</v>
+        <v>456546</v>
       </c>
       <c r="R9" t="n">
-        <v>6650919</v>
+        <v>6650834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,8 +1582,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1601,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118870529</v>
+        <v>118870530</v>
       </c>
       <c r="B10" t="n">
-        <v>90451</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456556</v>
+        <v>456548</v>
       </c>
       <c r="R10" t="n">
-        <v>6650879</v>
+        <v>6650892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,21 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118870528</v>
+        <v>118870533</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,25 +1730,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456560</v>
+        <v>456624</v>
       </c>
       <c r="R11" t="n">
-        <v>6650873</v>
+        <v>6651012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -1378,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118870529</v>
+        <v>118870527</v>
       </c>
       <c r="B8" t="n">
-        <v>90458</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,34 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456556</v>
+        <v>456546</v>
       </c>
       <c r="R8" t="n">
-        <v>6650879</v>
+        <v>6650834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,22 +1465,23 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1495,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118870527</v>
+        <v>118870529</v>
       </c>
       <c r="B9" t="n">
-        <v>79572</v>
+        <v>90458</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,37 +1515,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456546</v>
+        <v>456556</v>
       </c>
       <c r="R9" t="n">
-        <v>6650834</v>
+        <v>6650879</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,23 +1583,22 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 42882-2020 artfynd.xlsx
+++ b/artfynd/A 42882-2020 artfynd.xlsx
@@ -965,7 +965,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118870528</v>
+        <v>118870537</v>
       </c>
       <c r="B4" t="n">
         <v>78491</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456560</v>
+        <v>456603</v>
       </c>
       <c r="R4" t="n">
-        <v>6650873</v>
+        <v>6651057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118870537</v>
+        <v>118870529</v>
       </c>
       <c r="B6" t="n">
-        <v>78491</v>
+        <v>90458</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456603</v>
+        <v>456556</v>
       </c>
       <c r="R6" t="n">
-        <v>6651057</v>
+        <v>6650879</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,6 +1255,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1271,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118870536</v>
+        <v>118870533</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>90476</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,43 +1298,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456606</v>
+        <v>456624</v>
       </c>
       <c r="R7" t="n">
-        <v>6651051</v>
+        <v>6651012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118870527</v>
+        <v>118870528</v>
       </c>
       <c r="B8" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,37 +1404,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456546</v>
+        <v>456560</v>
       </c>
       <c r="R8" t="n">
-        <v>6650834</v>
+        <v>6650873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,24 +1472,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1499,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118870529</v>
+        <v>118870536</v>
       </c>
       <c r="B9" t="n">
-        <v>90458</v>
+        <v>57306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,34 +1506,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456556</v>
+        <v>456606</v>
       </c>
       <c r="R9" t="n">
-        <v>6650879</v>
+        <v>6651051</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,21 +1581,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1718,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118870533</v>
+        <v>118870527</v>
       </c>
       <c r="B11" t="n">
-        <v>90476</v>
+        <v>79572</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1711,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kullbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456624</v>
+        <v>456546</v>
       </c>
       <c r="R11" t="n">
-        <v>6651012</v>
+        <v>6650834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,8 +1786,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
